--- a/output/pdf_financials_xlsx/LOAN.xlsx
+++ b/output/pdf_financials_xlsx/LOAN.xlsx
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>6.559158</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.5206</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.467697</v>
       </c>
     </row>
     <row r="93">
@@ -3019,7 +3019,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>6.559158</v>
       </c>

--- a/output/pdf_financials_xlsx/LOAN.xlsx
+++ b/output/pdf_financials_xlsx/LOAN.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.025653</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.058715</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.036923</v>
       </c>
     </row>
     <row r="13">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.455906</v>
+        <v>-0.481559</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.546008</v>
+        <v>-0.604723</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.381152</v>
+        <v>-0.418075</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.455906</v>
+        <v>-0.481559</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.546008</v>
+        <v>-0.604723</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.381152</v>
+        <v>-0.418075</v>
       </c>
     </row>
     <row r="30">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
